--- a/data/satisfaction_detail/2026/6月/展览主承办.xlsx
+++ b/data/satisfaction_detail/2026/6月/展览主承办.xlsx
@@ -472,10 +472,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>9.91</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>10</v>
+        <v>9.710000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -485,10 +485,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>10</v>
+        <v>9.98</v>
       </c>
     </row>
     <row r="4">
@@ -579,7 +579,7 @@
         <v>10</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>10</v>
+        <v>9.83</v>
       </c>
     </row>
     <row r="11">
@@ -602,10 +602,10 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>10</v>
+        <v>9.83</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>10</v>
+        <v>9.83</v>
       </c>
     </row>
     <row r="13">
@@ -693,10 +693,10 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>9.74</v>
+        <v>9.59</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>10</v>
+        <v>9.880000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.67</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>10</v>
+        <v>9.83</v>
       </c>
     </row>
     <row r="21">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>9.6</v>
+        <v>9.33</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>10</v>
+        <v>9.83</v>
       </c>
     </row>
     <row r="22">
@@ -732,10 +732,10 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>10</v>
+        <v>9.67</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>10</v>
+        <v>9.83</v>
       </c>
     </row>
     <row r="23">
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>10</v>
+        <v>9.83</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>10</v>
+        <v>9.83</v>
       </c>
     </row>
     <row r="24">
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>10</v>
+        <v>9.83</v>
       </c>
     </row>
     <row r="25">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.83</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>10</v>
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.33</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>10</v>
@@ -797,10 +797,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>10</v>
+        <v>9.92</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>10</v>
+        <v>9.960000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -810,10 +810,10 @@
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>10</v>
+        <v>9.67</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>10</v>
+        <v>9.83</v>
       </c>
     </row>
     <row r="29">
@@ -861,8 +861,12 @@
           <t>智慧场馆</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr"/>
-      <c r="C32" s="3" t="inlineStr"/>
+      <c r="B32" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -879,8 +883,12 @@
           <t>室内导航系统</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr"/>
-      <c r="C34" s="4" t="inlineStr"/>
+      <c r="B34" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -888,8 +896,12 @@
           <t>寻车系统</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr"/>
-      <c r="C35" s="4" t="inlineStr"/>
+      <c r="B35" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
